--- a/Collections/EURO/France/#EURO#France#Regular#[1999-present]#circulation_quality.xlsx
+++ b/Collections/EURO/France/#EURO#France#Regular#[1999-present]#circulation_quality.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\France\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B225C1E9-3252-422A-A808-32EE9034E752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4964FC59-E41A-4549-A499-64B3BEBDC234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1cent" sheetId="4" r:id="rId1"/>
@@ -46,6 +46,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -388,7 +391,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="212">
   <si>
     <t>Year</t>
   </si>
@@ -922,21 +925,9 @@
     <t>27.500</t>
   </si>
   <si>
-    <t>24.500</t>
-  </si>
-  <si>
     <t>39.522</t>
   </si>
   <si>
-    <t>39.500</t>
-  </si>
-  <si>
-    <t>51.522</t>
-  </si>
-  <si>
-    <t>35.000</t>
-  </si>
-  <si>
     <t>Obv: Mint main engraving Symbol - Square</t>
   </si>
   <si>
@@ -965,6 +956,78 @@
   </si>
   <si>
     <t>Subtype_2#Map_of_Europe</t>
+  </si>
+  <si>
+    <t>101.330.000</t>
+  </si>
+  <si>
+    <t>214.222.500</t>
+  </si>
+  <si>
+    <t>160.135.000</t>
+  </si>
+  <si>
+    <t>133.922.000</t>
+  </si>
+  <si>
+    <t>134.976.000</t>
+  </si>
+  <si>
+    <t>89.720.000</t>
+  </si>
+  <si>
+    <t>54.022.500</t>
+  </si>
+  <si>
+    <t>82.106.000</t>
+  </si>
+  <si>
+    <t>83.283.500</t>
+  </si>
+  <si>
+    <t>80.322.500</t>
+  </si>
+  <si>
+    <t>40.455.800</t>
+  </si>
+  <si>
+    <t>42.794.000</t>
+  </si>
+  <si>
+    <t>68.222.500</t>
+  </si>
+  <si>
+    <t>40.268.600</t>
+  </si>
+  <si>
+    <t>22.226.000</t>
+  </si>
+  <si>
+    <t>18.322.500</t>
+  </si>
+  <si>
+    <t>35.555.000</t>
+  </si>
+  <si>
+    <t>22.000</t>
+  </si>
+  <si>
+    <t>32.500</t>
+  </si>
+  <si>
+    <t>54.544</t>
+  </si>
+  <si>
+    <t>18.087.940</t>
+  </si>
+  <si>
+    <t>7.559.522</t>
+  </si>
+  <si>
+    <t>30.053.544</t>
+  </si>
+  <si>
+    <t>40.525</t>
   </si>
 </sst>
 </file>
@@ -974,7 +1037,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0\ [$€-1];[Red]\-#,##0\ [$€-1]"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1036,6 +1099,10 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1276,15 +1343,14 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="23">
+  <dxfs count="24">
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -1446,6 +1512,15 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1477,9 +1552,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="22" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -1748,7 +1823,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -1779,13 +1854,13 @@
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="29"/>
       <c r="B2" s="27" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E2" s="24" t="s">
         <v>27</v>
@@ -2315,7 +2390,7 @@
         <v>175</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -2336,10 +2411,10 @@
         <v>28</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -2360,10 +2435,10 @@
         <v>28</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -2384,11 +2459,9 @@
         <v>28</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>181</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="E27" s="11"/>
       <c r="F27" s="1">
         <v>0</v>
       </c>
@@ -2408,7 +2481,7 @@
         <v>28</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E28" s="11"/>
       <c r="F28" s="1">
@@ -2416,6 +2489,28 @@
       </c>
       <c r="G28" s="3" t="str">
         <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="E29" s="11"/>
+      <c r="F29" s="1">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3" t="str">
+        <f t="shared" ref="G29" si="4">IF(OR(AND(F29&gt;1,F29&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -2427,7 +2522,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3:F5 F7:F22 F24 F26 F28">
-    <cfRule type="containsText" dxfId="22" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="20" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
@@ -2442,7 +2537,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="containsText" dxfId="21" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="19" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F6))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -2456,8 +2551,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F25 F23 F27">
-    <cfRule type="containsText" dxfId="20" priority="1" operator="containsText" text="*-">
+  <conditionalFormatting sqref="F23 F25 F27 F29">
+    <cfRule type="containsText" dxfId="18" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F23))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
@@ -2479,7 +2574,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -2510,13 +2605,13 @@
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="29"/>
       <c r="B2" s="27" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E2" s="24" t="s">
         <v>27</v>
@@ -3046,7 +3141,7 @@
         <v>175</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -3067,10 +3162,10 @@
         <v>28</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -3091,10 +3186,10 @@
         <v>28</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -3115,11 +3210,9 @@
         <v>28</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>181</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="E27" s="11"/>
       <c r="F27" s="1">
         <v>0</v>
       </c>
@@ -3139,7 +3232,7 @@
         <v>28</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E28" s="11"/>
       <c r="F28" s="1">
@@ -3147,6 +3240,28 @@
       </c>
       <c r="G28" s="3" t="str">
         <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="E29" s="11"/>
+      <c r="F29" s="1">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3" t="str">
+        <f t="shared" ref="G29" si="3">IF(OR(AND(F29&gt;1,F29&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -3158,10 +3273,10 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3:F22">
-    <cfRule type="containsText" dxfId="19" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="17" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
-    <cfRule type="colorScale" priority="6">
+    <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -3173,8 +3288,23 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F23:F28">
-    <cfRule type="containsText" dxfId="18" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="16" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F23))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F29">
+    <cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F29))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
       <colorScale>
@@ -3195,7 +3325,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -3226,13 +3356,13 @@
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="29"/>
       <c r="B2" s="27" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E2" s="24" t="s">
         <v>27</v>
@@ -3762,7 +3892,7 @@
         <v>175</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -3783,10 +3913,10 @@
         <v>28</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -3807,10 +3937,10 @@
         <v>28</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -3831,11 +3961,9 @@
         <v>28</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>181</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="E27" s="11"/>
       <c r="F27" s="1">
         <v>0</v>
       </c>
@@ -3855,7 +3983,7 @@
         <v>28</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E28" s="11"/>
       <c r="F28" s="1">
@@ -3863,6 +3991,28 @@
       </c>
       <c r="G28" s="3" t="str">
         <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="E29" s="11"/>
+      <c r="F29" s="1">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3" t="str">
+        <f t="shared" ref="G29" si="3">IF(OR(AND(F29&gt;1,F29&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -3874,7 +4024,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3:F22">
-    <cfRule type="containsText" dxfId="17" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="14" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
@@ -3888,8 +4038,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F23:F28">
-    <cfRule type="containsText" dxfId="16" priority="1" operator="containsText" text="*-">
+  <conditionalFormatting sqref="F23:F29">
+    <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F23))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
@@ -3911,7 +4061,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -3943,16 +4093,16 @@
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="29"/>
       <c r="B2" s="27" t="s">
+        <v>183</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>191</v>
-      </c>
       <c r="E2" s="6" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F2" s="24" t="s">
         <v>27</v>
@@ -4546,7 +4696,7 @@
         <v>175</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="G24" s="1">
         <v>0</v>
@@ -4570,10 +4720,10 @@
         <v>8</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="G25" s="1">
         <v>0</v>
@@ -4597,10 +4747,10 @@
         <v>8</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="G26" s="1">
         <v>0</v>
@@ -4624,11 +4774,9 @@
         <v>8</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="F27" s="11" t="s">
-        <v>181</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="F27" s="11"/>
       <c r="G27" s="1">
         <v>0</v>
       </c>
@@ -4642,7 +4790,7 @@
         <v>2024</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C28" s="23" t="s">
         <v>28</v>
@@ -4651,7 +4799,7 @@
         <v>8</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F28" s="11"/>
       <c r="G28" s="1">
@@ -4659,6 +4807,31 @@
       </c>
       <c r="H28" s="3" t="str">
         <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="C29" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="F29" s="11"/>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3" t="str">
+        <f t="shared" ref="H29" si="4">IF(OR(AND(G29&gt;1,G29&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -4670,7 +4843,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="G3:G22">
-    <cfRule type="containsText" dxfId="15" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="12" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4686,12 +4859,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G23:G28">
-    <cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="*-">
+  <conditionalFormatting sqref="G23:G29">
+    <cfRule type="containsText" dxfId="11" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G23))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G23:G28">
+  <conditionalFormatting sqref="G23:G29">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4711,7 +4884,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -4743,16 +4916,16 @@
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="29"/>
       <c r="B2" s="27" t="s">
+        <v>183</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>191</v>
-      </c>
       <c r="E2" s="6" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F2" s="24" t="s">
         <v>27</v>
@@ -5348,7 +5521,7 @@
         <v>175</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="G24" s="1">
         <v>0</v>
@@ -5372,10 +5545,10 @@
         <v>8</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="G25" s="1">
         <v>0</v>
@@ -5399,10 +5572,10 @@
         <v>8</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="G26" s="1">
         <v>0</v>
@@ -5426,11 +5599,9 @@
         <v>8</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="F27" s="11" t="s">
-        <v>181</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="F27" s="11"/>
       <c r="G27" s="1">
         <v>0</v>
       </c>
@@ -5444,7 +5615,7 @@
         <v>2024</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C28" s="23" t="s">
         <v>28</v>
@@ -5453,7 +5624,7 @@
         <v>8</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F28" s="11"/>
       <c r="G28" s="1">
@@ -5461,6 +5632,31 @@
       </c>
       <c r="H28" s="3" t="str">
         <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="C29" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="F29" s="11"/>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3" t="str">
+        <f t="shared" ref="H29" si="3">IF(OR(AND(G29&gt;1,G29&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -5472,7 +5668,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="G3:G22">
-    <cfRule type="containsText" dxfId="13" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="10" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5488,12 +5684,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G23:G28">
-    <cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="*-">
+  <conditionalFormatting sqref="G23:G29">
+    <cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G23))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G23:G28">
+  <conditionalFormatting sqref="G23:G29">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5513,7 +5709,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -5545,16 +5741,16 @@
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="29"/>
       <c r="B2" s="27" t="s">
+        <v>183</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>191</v>
-      </c>
       <c r="E2" s="6" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F2" s="24" t="s">
         <v>27</v>
@@ -6150,7 +6346,7 @@
         <v>175</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="G24" s="1">
         <v>0</v>
@@ -6174,10 +6370,10 @@
         <v>8</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>176</v>
+        <v>203</v>
       </c>
       <c r="G25" s="1">
         <v>0</v>
@@ -6201,10 +6397,10 @@
         <v>8</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="G26" s="1">
         <v>0</v>
@@ -6228,11 +6424,9 @@
         <v>8</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="F27" s="11" t="s">
-        <v>181</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="F27" s="11"/>
       <c r="G27" s="1">
         <v>0</v>
       </c>
@@ -6246,7 +6440,7 @@
         <v>2024</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C28" s="23" t="s">
         <v>28</v>
@@ -6255,7 +6449,7 @@
         <v>8</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F28" s="11"/>
       <c r="G28" s="1">
@@ -6263,6 +6457,31 @@
       </c>
       <c r="H28" s="3" t="str">
         <f t="shared" ref="H28" si="2">IF(OR(AND(G28&gt;1,G28&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="C29" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="F29" s="11"/>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3" t="str">
+        <f t="shared" ref="H29" si="3">IF(OR(AND(G29&gt;1,G29&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -6273,12 +6492,12 @@
     <mergeCell ref="C1:E1"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
-  <conditionalFormatting sqref="G3:G22 G24 G26 G28">
-    <cfRule type="containsText" dxfId="11" priority="3" operator="containsText" text="*-">
+  <conditionalFormatting sqref="G3:G22 G24 G26 G28:G29">
+    <cfRule type="containsText" dxfId="8" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3:G22 G24 G26 G28">
+  <conditionalFormatting sqref="G3:G22 G24 G26 G28:G29">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6291,11 +6510,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G23 G25 G27">
-    <cfRule type="containsText" dxfId="10" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G23))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G25 G23 G27">
+  <conditionalFormatting sqref="G23 G25 G27">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6315,7 +6534,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -6347,16 +6566,16 @@
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="29"/>
       <c r="B2" s="27" t="s">
+        <v>183</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>191</v>
-      </c>
       <c r="E2" s="6" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F2" s="24" t="s">
         <v>27</v>
@@ -6952,7 +7171,7 @@
       <c r="E24" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="F24" s="25" t="s">
         <v>176</v>
       </c>
       <c r="G24" s="1">
@@ -6977,10 +7196,10 @@
         <v>7</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="F25" s="11" t="s">
         <v>178</v>
+      </c>
+      <c r="F25" s="25" t="s">
+        <v>177</v>
       </c>
       <c r="G25" s="1">
         <v>0</v>
@@ -6995,7 +7214,7 @@
         <v>2022</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>31</v>
+        <v>179</v>
       </c>
       <c r="C26" s="23" t="s">
         <v>28</v>
@@ -7004,10 +7223,10 @@
         <v>7</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="F26" s="11" t="s">
-        <v>180</v>
+        <v>178</v>
+      </c>
+      <c r="F26" s="25" t="s">
+        <v>207</v>
       </c>
       <c r="G26" s="1">
         <v>0</v>
@@ -7022,7 +7241,7 @@
         <v>2023</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C27" s="23" t="s">
         <v>28</v>
@@ -7031,10 +7250,10 @@
         <v>7</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="F27" s="11" t="s">
-        <v>181</v>
+        <v>178</v>
+      </c>
+      <c r="F27" s="25" t="s">
+        <v>206</v>
       </c>
       <c r="G27" s="1">
         <v>0</v>
@@ -7049,7 +7268,7 @@
         <v>2024</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C28" s="23" t="s">
         <v>28</v>
@@ -7058,14 +7277,43 @@
         <v>7</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="F28" s="11"/>
+        <v>178</v>
+      </c>
+      <c r="F28" s="25" t="s">
+        <v>205</v>
+      </c>
       <c r="G28" s="1">
         <v>0</v>
       </c>
       <c r="H28" s="3" t="str">
-        <f t="shared" ref="H28" si="3">IF(OR(AND(G28&gt;1,G28&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="H28:H29" si="3">IF(OR(AND(G28&gt;1,G28&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="C29" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="F29" s="25" t="s">
+        <v>211</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3" t="str">
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -7075,8 +7323,9 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:E1"/>
   </mergeCells>
+  <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="G3:G22">
-    <cfRule type="containsText" dxfId="9" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7093,7 +7342,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G23">
-    <cfRule type="containsText" dxfId="8" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G23))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7109,12 +7358,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G24:G27">
-    <cfRule type="containsText" dxfId="7" priority="3" operator="containsText" text="*-">
+  <conditionalFormatting sqref="G24:G27 G29">
+    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G24))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G24:G27">
+  <conditionalFormatting sqref="G24:G27 G29">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -7127,7 +7376,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G28">
-    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G28))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7183,16 +7432,16 @@
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="29"/>
       <c r="B2" s="27" t="s">
+        <v>183</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>191</v>
-      </c>
       <c r="E2" s="6" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F2" s="24" t="s">
         <v>27</v>
@@ -7791,7 +8040,7 @@
         <v>175</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="G24" s="1">
         <v>0</v>
@@ -7815,10 +8064,10 @@
         <v>8</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>178</v>
+        <v>209</v>
       </c>
       <c r="G25" s="1">
         <v>0</v>
@@ -7833,7 +8082,7 @@
         <v>2022</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>31</v>
+        <v>179</v>
       </c>
       <c r="C26" s="23" t="s">
         <v>28</v>
@@ -7842,10 +8091,10 @@
         <v>8</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="G26" s="1">
         <v>0</v>
@@ -7860,7 +8109,7 @@
         <v>2023</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C27" s="23" t="s">
         <v>28</v>
@@ -7869,11 +8118,9 @@
         <v>8</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="F27" s="11" t="s">
-        <v>181</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="F27" s="11"/>
       <c r="G27" s="1">
         <v>0</v>
       </c>
@@ -7887,7 +8134,7 @@
         <v>2024</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C28" s="23" t="s">
         <v>28</v>
@@ -7896,18 +8143,41 @@
         <v>8</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F28" s="11"/>
       <c r="G28" s="1">
         <v>0</v>
       </c>
       <c r="H28" s="3" t="str">
-        <f t="shared" ref="H28" si="4">IF(OR(AND(G28&gt;1,G28&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="H28:H29" si="4">IF(OR(AND(G28&gt;1,G28&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
     <row r="29" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="8">
+        <v>2025</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="C29" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="F29" s="11"/>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="R29" s="26"/>
       <c r="S29" s="26"/>
     </row>
@@ -7927,7 +8197,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="G3:G22 G24 G26">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7943,12 +8213,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G23 G25 G27">
-    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
+  <conditionalFormatting sqref="G23 G25 G27 G29">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G23))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G25 G23 G27">
+  <conditionalFormatting sqref="G23 G25 G27 G29">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -7961,7 +8231,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G28">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G28))))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Collections/EURO/France/#EURO#France#Regular#[1999-present]#circulation_quality.xlsx
+++ b/Collections/EURO/France/#EURO#France#Regular#[1999-present]#circulation_quality.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\France\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4964FC59-E41A-4549-A499-64B3BEBDC234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01AB7490-3380-473B-B6B4-1F57411F22C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1cent" sheetId="4" r:id="rId1"/>
@@ -1345,6 +1345,15 @@
   </cellStyles>
   <dxfs count="24">
     <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF9BE5FF"/>
@@ -1512,15 +1521,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1552,9 +1552,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="22" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="21"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -2522,7 +2522,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3:F5 F7:F22 F24 F26 F28">
-    <cfRule type="containsText" dxfId="20" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="23" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
@@ -2537,7 +2537,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="containsText" dxfId="19" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="22" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F6))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -2551,8 +2551,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F23 F25 F27 F29">
-    <cfRule type="containsText" dxfId="18" priority="1" operator="containsText" text="*-">
+  <conditionalFormatting sqref="F25 F23 F27 F29">
+    <cfRule type="containsText" dxfId="21" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F23))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
@@ -3273,7 +3273,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3:F22">
-    <cfRule type="containsText" dxfId="17" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="20" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="8">
@@ -3288,7 +3288,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F23:F28">
-    <cfRule type="containsText" dxfId="16" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="19" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F23))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -3303,7 +3303,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F29">
-    <cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="18" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F29))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
@@ -4024,7 +4024,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3:F22">
-    <cfRule type="containsText" dxfId="14" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="17" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
@@ -4039,7 +4039,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F23:F29">
-    <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="16" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F23))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
@@ -4843,7 +4843,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="G3:G22">
-    <cfRule type="containsText" dxfId="12" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="15" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4860,7 +4860,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G23:G29">
-    <cfRule type="containsText" dxfId="11" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G23))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5011,7 +5011,7 @@
         <v>115</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5668,7 +5668,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="G3:G22">
-    <cfRule type="containsText" dxfId="10" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="13" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5685,7 +5685,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G23:G29">
-    <cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G23))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6493,7 +6493,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="G3:G22 G24 G26 G28:G29">
-    <cfRule type="containsText" dxfId="8" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="11" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6510,11 +6510,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G23 G25 G27">
-    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="10" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G23))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G23 G25 G27">
+  <conditionalFormatting sqref="G25 G23 G27">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -7325,7 +7325,7 @@
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="G3:G22">
-    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="9" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7342,7 +7342,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G23">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="8" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G23))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7359,7 +7359,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G24:G27 G29">
-    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="7" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G24))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7376,7 +7376,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G28">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G28))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7471,7 +7471,7 @@
         <v>150</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" s="3" t="str">
         <f t="shared" ref="H3:H22" si="0">IF(OR(AND(G3&gt;1,G3&lt;&gt;"-")),"Can exchange","")</f>
@@ -8197,7 +8197,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="G3:G22 G24 G26">
-    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8214,11 +8214,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G23 G25 G27 G29">
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G23))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G23 G25 G27 G29">
+  <conditionalFormatting sqref="G25 G23 G27 G29">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -8231,7 +8231,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G28">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G28))))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Collections/EURO/France/#EURO#France#Regular#[1999-present]#circulation_quality.xlsx
+++ b/Collections/EURO/France/#EURO#France#Regular#[1999-present]#circulation_quality.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\France\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01AB7490-3380-473B-B6B4-1F57411F22C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13D4DD6F-46EE-4468-9AF2-3FC242DEA430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1cent" sheetId="4" r:id="rId1"/>
@@ -2273,7 +2273,7 @@
         <v>49</v>
       </c>
       <c r="F19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" s="3" t="str">
         <f t="shared" si="1"/>
@@ -2551,7 +2551,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F25 F23 F27 F29">
+  <conditionalFormatting sqref="F23 F25 F27 F29">
     <cfRule type="containsText" dxfId="21" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F23))))</formula>
     </cfRule>
@@ -6514,7 +6514,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(G23))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G25 G23 G27">
+  <conditionalFormatting sqref="G23 G25 G27">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -8218,7 +8218,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(G23))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G25 G23 G27 G29">
+  <conditionalFormatting sqref="G23 G25 G27 G29">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
